--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>95.39500184125299</v>
+        <v>15.50168779920361</v>
       </c>
       <c r="D2" t="n">
-        <v>95.69965911236778</v>
+        <v>15.55119460575976</v>
       </c>
       <c r="E2" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F2" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>81.17887673563325</v>
+        <v>13.1915674695404</v>
       </c>
       <c r="D3" t="n">
-        <v>81.38511827813787</v>
+        <v>13.2250817201974</v>
       </c>
       <c r="E3" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F3" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.45251969596097</v>
+        <v>10.47353445059366</v>
       </c>
       <c r="D4" t="n">
-        <v>64.75494686737811</v>
+        <v>10.52267886594894</v>
       </c>
       <c r="E4" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F4" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.69998079789288</v>
+        <v>10.67624687965759</v>
       </c>
       <c r="D5" t="n">
-        <v>65.98902184213169</v>
+        <v>10.7232160493464</v>
       </c>
       <c r="E5" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F5" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.64766924711192</v>
+        <v>6.442746252655687</v>
       </c>
       <c r="D6" t="n">
-        <v>39.95155914088706</v>
+        <v>6.492128360394148</v>
       </c>
       <c r="E6" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F6" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>75.58163538160528</v>
+        <v>12.28201574951086</v>
       </c>
       <c r="D7" t="n">
-        <v>75.46746102553669</v>
+        <v>12.26346241664971</v>
       </c>
       <c r="E7" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F7" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>59.77807455642511</v>
+        <v>9.71393711541908</v>
       </c>
       <c r="D8" t="n">
-        <v>59.97513515729769</v>
+        <v>9.745959463060874</v>
       </c>
       <c r="E8" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F8" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>64.47972313499635</v>
+        <v>10.47795500943691</v>
       </c>
       <c r="D9" t="n">
-        <v>64.64849611764515</v>
+        <v>10.50538061911734</v>
       </c>
       <c r="E9" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F9" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>77.54999197228371</v>
+        <v>12.6018736954961</v>
       </c>
       <c r="D10" t="n">
-        <v>77.29416820365984</v>
+        <v>12.56030233309472</v>
       </c>
       <c r="E10" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F10" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.256236557849183</v>
+        <v>1.016638440650492</v>
       </c>
       <c r="D11" t="n">
-        <v>6.314445519776239</v>
+        <v>1.026097396963639</v>
       </c>
       <c r="E11" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F11" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.59573064568249</v>
+        <v>5.784306229923406</v>
       </c>
       <c r="D12" t="n">
-        <v>35.73997312551236</v>
+        <v>5.807745632895759</v>
       </c>
       <c r="E12" t="n">
-        <v>23.77906570566171</v>
+        <v>3.864098177170029</v>
       </c>
       <c r="F12" t="n">
-        <v>23.77564702381873</v>
+        <v>3.863542641370544</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
